--- a/Use-Case_Description--Process_Uploaded_Audio_Files.xlsx
+++ b/Use-Case_Description--Process_Uploaded_Audio_Files.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\thoma\Documents\GitHub\Audio_Analyzer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CC3155E-744C-4C3F-B3F7-14CC481040E6}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E681C54-E532-45A4-9A1C-CC83C9F4BA45}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="100" yWindow="80" windowWidth="19120" windowHeight="20670" xr2:uid="{F029340B-59BC-4187-9937-02EC323D7EB9}"/>
+    <workbookView xWindow="4180" yWindow="930" windowWidth="19060" windowHeight="20670" xr2:uid="{F029340B-59BC-4187-9937-02EC323D7EB9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="55">
   <si>
     <t>Use-Case Name</t>
   </si>
@@ -281,6 +281,9 @@
 (6) Status of "successful processing" for each audio file
 (AF1-5.2) Status of "abandoned processing" for an audio file
 (AF2-5.2) Status of "failed processing" for an audio file</t>
+  </si>
+  <si>
+    <t>Grant Permission</t>
   </si>
 </sst>
 </file>
@@ -876,7 +879,7 @@
         <v>11</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="C21" s="11" t="s">
         <v>17</v>

--- a/Use-Case_Description--Process_Uploaded_Audio_Files.xlsx
+++ b/Use-Case_Description--Process_Uploaded_Audio_Files.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\thoma\Documents\GitHub\Audio_Analyzer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E681C54-E532-45A4-9A1C-CC83C9F4BA45}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5FFFA5E-8D12-4F7E-9FD7-B532B87A255D}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4180" yWindow="930" windowWidth="19060" windowHeight="20670" xr2:uid="{F029340B-59BC-4187-9937-02EC323D7EB9}"/>
+    <workbookView xWindow="130" yWindow="130" windowWidth="19060" windowHeight="20670" xr2:uid="{F029340B-59BC-4187-9937-02EC323D7EB9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="54">
   <si>
     <t>Use-Case Name</t>
   </si>
@@ -204,8 +204,13 @@
     <t>At least one audio file for which the Worker has permission to process has been uploaded.</t>
   </si>
   <si>
-    <t>1. The Worker signals desire to select uploaded audio files for which they have permission to process
-for processing.
+    <t>Worker: (1) Signal desire to process one or more audio files.
+Worker: (3) Selection of one or more audio files for processing.
+Worker: (4) Signal to process the audio files.
+Worker: (AF1-5.1) Signal to abandon processing an audio file.</t>
+  </si>
+  <si>
+    <t>1. The Worker signals desire to select uploaded audio files for processing.
 2. The system provides to the Worker the set of all unprocessed uploaded audio files for which the Worker has permission to process.
 3. The Worker selects one or more audio files for processing.
 4. The Worker requests that the system process the selected audio file(s).
@@ -222,7 +227,8 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Alternate Flow 1:</t>
+      <t xml:space="preserve">Alternate Flow 1:
+</t>
     </r>
     <r>
       <rPr>
@@ -232,9 +238,9 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">
-5.1. The Worker abandons processing one or more audio files.
-5.2. The system provides a status of "abandoned processing" to the Worker for that audio file.
+      <t xml:space="preserve">5.1. The Worker signals that processing of an audio file in the group of audio files being uploaded should be abandoned.
+5.2. The system removes the abandoned audio file from the group of audio files being processed.
+5.3. The status of the audio file that was abandoned becomes "abandoned processing".
 </t>
     </r>
     <r>
@@ -246,15 +252,14 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>This use case terminates after some combination of the main flow and the alternate flows complete
-for each audio file.</t>
+      <t>This use case continues at step 5 of the main flow.</t>
     </r>
   </si>
   <si>
     <r>
       <t xml:space="preserve">Alternate Flow 2:
 5.1. The system fails to process an audio file.
-5.2. The system provides a status of "failed processing" to the Worker for that audio file.
+5.2. The status of the audio file whose processing failed becomes "failed processing".
 </t>
     </r>
     <r>
@@ -266,24 +271,12 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>This use case terminates after some combination of the main flow and the alternate flows complete
-for each audio file.</t>
+      <t>This use case continues at step 5 of the main flow.</t>
     </r>
   </si>
   <si>
-    <t>Worker: (1) Signal desire to process one or more audio files.
-Worker: (3) Selection of one or more audio files for processing.
-Worker: (4) Signal to process the audio files.
-Worker: (AF1-5.1) Signal to abandon processing an audio file.</t>
-  </si>
-  <si>
     <t>(2) Set of all unprocessed uploaded audio files for which the Worker has permission to process.
-(6) Status of "successful processing" for each audio file
-(AF1-5.2) Status of "abandoned processing" for an audio file
-(AF2-5.2) Status of "failed processing" for an audio file</t>
-  </si>
-  <si>
-    <t>Grant Permission</t>
+(6) Status of "successful processing" for all processed audio files, "abandoned processing" for all audio files whose status were set to "abandoned processing", and "failed upload" for all audio files whose status were set to "failed upload".</t>
   </si>
 </sst>
 </file>
@@ -850,28 +843,28 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="116" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:3" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A18" s="4" t="s">
         <v>25</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C18" s="10" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:3" ht="87" x14ac:dyDescent="0.35">
       <c r="A19" s="4" t="s">
         <v>26</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" ht="72.5" x14ac:dyDescent="0.35">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="58" x14ac:dyDescent="0.35">
       <c r="B20" s="6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
@@ -879,7 +872,7 @@
         <v>11</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="C21" s="11" t="s">
         <v>17</v>
@@ -901,7 +894,7 @@
         <v>13</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C23" s="11" t="s">
         <v>19</v>
